--- a/xlsx/packagedata template-alt4.xlsx
+++ b/xlsx/packagedata template-alt4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Collection\ReactThreejsFiber\Containerloadingsys\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DDD71A-2D26-4D96-8579-85DAE0D121C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4919C8BC-2DD2-45AB-8E76-AD95A9DDC8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -577,7 +577,7 @@
         <v>14</v>
       </c>
       <c r="H2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2" t="s">
         <v>23</v>
@@ -621,7 +621,7 @@
         <v>17</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3" t="s">
         <v>23</v>

--- a/xlsx/packagedata template-alt4.xlsx
+++ b/xlsx/packagedata template-alt4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Collection\ReactThreejsFiber\Containerloadingsys\public\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4919C8BC-2DD2-45AB-8E76-AD95A9DDC8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089759A8-53DD-40BD-B8A0-8BC04AE1BB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -500,7 +500,7 @@
   <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.1640625" bestFit="1" customWidth="1"/>
@@ -592,7 +592,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N2" t="s">
         <v>21</v>
@@ -636,7 +636,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N3" t="s">
         <v>21</v>
